--- a/2022 data/excel_outputs/262_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/262_boothwise_data.xlsx
@@ -14,11 +14,74 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="484">
   <si>
     <t>AC 262 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
@@ -469,7 +532,7 @@
     <t>RAJKIYA CORPANTARY SCHOOL NEW KATRA ROOM NO.-4</t>
   </si>
   <si>
-    <t>■■■■■■ ■■■■■■■■■■■ ■■■■■ ■■■■ ■■■■ ■■■■ ■■.-5 RAJKIYA CORPANTARY SCHOOL NEW KATRA ROOM NO.-5</t>
+    <t>MI8DAYAM KAE DI0 PI0 GABS NAM I00-3KA0 IMIDLAS</t>
   </si>
   <si>
     <t>RAJKIYA CORPANTARY SCHOOL NEW KATRA ROOM NO.-6</t>
@@ -1409,8 +1472,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1426,7 +1497,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1434,12 +1505,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1738,76 +1827,139 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="D2" t="s">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="E2" t="s">
-        <v>445</v>
+        <v>466</v>
       </c>
       <c r="F2" t="s">
-        <v>446</v>
+        <v>467</v>
       </c>
       <c r="G2" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="H2" t="s">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="I2" t="s">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="J2" t="s">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="K2" t="s">
-        <v>451</v>
+        <v>472</v>
       </c>
       <c r="L2" t="s">
-        <v>452</v>
+        <v>473</v>
       </c>
       <c r="M2" t="s">
-        <v>453</v>
+        <v>474</v>
       </c>
       <c r="N2" t="s">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="O2" t="s">
-        <v>455</v>
+        <v>476</v>
       </c>
       <c r="P2" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="Q2" t="s">
-        <v>457</v>
+        <v>478</v>
       </c>
       <c r="R2" t="s">
-        <v>458</v>
+        <v>479</v>
       </c>
       <c r="S2" t="s">
-        <v>459</v>
+        <v>480</v>
       </c>
       <c r="T2" t="s">
-        <v>460</v>
+        <v>481</v>
       </c>
       <c r="U2" t="s">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="V2" t="s">
-        <v>462</v>
+        <v>483</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -1815,7 +1967,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="C3">
         <v>727</v>
@@ -1883,7 +2035,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="C4">
         <v>767</v>
@@ -1951,7 +2103,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="C5">
         <v>1046</v>
@@ -2019,7 +2171,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="C6">
         <v>1063</v>
@@ -2087,7 +2239,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C7">
         <v>1028</v>
@@ -2155,7 +2307,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C8">
         <v>846</v>
@@ -2223,7 +2375,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C9">
         <v>899</v>
@@ -2291,7 +2443,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C10">
         <v>720</v>
@@ -2359,7 +2511,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C11">
         <v>1037</v>
@@ -2427,7 +2579,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>889</v>
@@ -2495,7 +2647,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>838</v>
@@ -2563,7 +2715,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>1080</v>
@@ -2631,7 +2783,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C15">
         <v>704</v>
@@ -2699,7 +2851,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C16">
         <v>843</v>
@@ -2767,7 +2919,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C17">
         <v>779</v>
@@ -2835,7 +2987,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C18">
         <v>894</v>
@@ -2903,7 +3055,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="C19">
         <v>1211</v>
@@ -2971,7 +3123,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C20">
         <v>1008</v>
@@ -3039,7 +3191,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="C21">
         <v>907</v>
@@ -3107,7 +3259,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C22">
         <v>1108</v>
@@ -3175,7 +3327,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="C23">
         <v>974</v>
@@ -3243,7 +3395,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C24">
         <v>1161</v>
@@ -3311,7 +3463,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C25">
         <v>1116</v>
@@ -3379,7 +3531,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="C26">
         <v>1113</v>
@@ -3447,7 +3599,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="C27">
         <v>1137</v>
@@ -3515,7 +3667,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C28">
         <v>901</v>
@@ -3583,7 +3735,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C29">
         <v>842</v>
@@ -3651,7 +3803,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="C30">
         <v>1068</v>
@@ -3719,7 +3871,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="C31">
         <v>727</v>
@@ -3787,7 +3939,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C32">
         <v>665</v>
@@ -3855,7 +4007,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C33">
         <v>795</v>
@@ -3923,7 +4075,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="C34">
         <v>1110</v>
@@ -3991,7 +4143,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C35">
         <v>1148</v>
@@ -4059,7 +4211,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="C36">
         <v>1196</v>
@@ -4127,7 +4279,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="C37">
         <v>1184</v>
@@ -4195,7 +4347,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="C38">
         <v>1212</v>
@@ -4263,7 +4415,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="C39">
         <v>1193</v>
@@ -4331,7 +4483,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="C40">
         <v>1119</v>
@@ -4399,7 +4551,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="C41">
         <v>1193</v>
@@ -4467,7 +4619,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="C42">
         <v>1239</v>
@@ -4535,7 +4687,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>64</v>
       </c>
       <c r="C43">
         <v>1001</v>
@@ -4603,7 +4755,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="C44">
         <v>831</v>
@@ -4671,7 +4823,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>66</v>
       </c>
       <c r="C45">
         <v>1187</v>
@@ -4739,7 +4891,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="C46">
         <v>1146</v>
@@ -4807,7 +4959,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C47">
         <v>1141</v>
@@ -4875,7 +5027,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="C48">
         <v>896</v>
@@ -4943,7 +5095,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="C49">
         <v>974</v>
@@ -5011,7 +5163,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="C50">
         <v>1232</v>
@@ -5079,7 +5231,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C51">
         <v>1227</v>
@@ -5147,7 +5299,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>52</v>
+        <v>73</v>
       </c>
       <c r="C52">
         <v>809</v>
@@ -5215,7 +5367,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="C53">
         <v>1207</v>
@@ -5283,7 +5435,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="C54">
         <v>461</v>
@@ -5351,7 +5503,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C55">
         <v>1204</v>
@@ -5419,7 +5571,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="C56">
         <v>1224</v>
@@ -5487,7 +5639,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C57">
         <v>1192</v>
@@ -5555,7 +5707,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="C58">
         <v>1169</v>
@@ -5623,7 +5775,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C59">
         <v>1128</v>
@@ -5691,7 +5843,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>81</v>
       </c>
       <c r="C60">
         <v>1156</v>
@@ -5759,7 +5911,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C61">
         <v>894</v>
@@ -5827,7 +5979,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="C62">
         <v>997</v>
@@ -5895,7 +6047,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
       <c r="C63">
         <v>856</v>
@@ -5963,7 +6115,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C64">
         <v>949</v>
@@ -6031,7 +6183,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C65">
         <v>1043</v>
@@ -6099,7 +6251,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="C66">
         <v>1087</v>
@@ -6167,7 +6319,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="C67">
         <v>1124</v>
@@ -6235,7 +6387,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="C68">
         <v>813</v>
@@ -6303,7 +6455,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C69">
         <v>827</v>
@@ -6371,7 +6523,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="C70">
         <v>1187</v>
@@ -6439,7 +6591,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>92</v>
       </c>
       <c r="C71">
         <v>1186</v>
@@ -6507,7 +6659,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>72</v>
+        <v>93</v>
       </c>
       <c r="C72">
         <v>1100</v>
@@ -6575,7 +6727,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C73">
         <v>1174</v>
@@ -6643,7 +6795,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="C74">
         <v>939</v>
@@ -6711,7 +6863,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="C75">
         <v>993</v>
@@ -6779,7 +6931,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="C76">
         <v>616</v>
@@ -6847,7 +6999,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="C77">
         <v>1009</v>
@@ -6915,7 +7067,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C78">
         <v>1146</v>
@@ -6983,7 +7135,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="C79">
         <v>816</v>
@@ -7051,7 +7203,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="C80">
         <v>1118</v>
@@ -7119,7 +7271,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="C81">
         <v>1172</v>
@@ -7187,7 +7339,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C82">
         <v>896</v>
@@ -7255,7 +7407,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C83">
         <v>768</v>
@@ -7323,7 +7475,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="C84">
         <v>799</v>
@@ -7391,7 +7543,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="C85">
         <v>913</v>
@@ -7459,7 +7611,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="C86">
         <v>714</v>
@@ -7527,7 +7679,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="C87">
         <v>847</v>
@@ -7595,7 +7747,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="C88">
         <v>655</v>
@@ -7663,7 +7815,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="C89">
         <v>1077</v>
@@ -7731,7 +7883,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="C90">
         <v>1101</v>
@@ -7799,7 +7951,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="C91">
         <v>830</v>
@@ -7867,7 +8019,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C92">
         <v>1210</v>
@@ -7935,7 +8087,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="C93">
         <v>886</v>
@@ -8003,7 +8155,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="C94">
         <v>1105</v>
@@ -8071,7 +8223,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="C95">
         <v>1111</v>
@@ -8139,7 +8291,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="C96">
         <v>1011</v>
@@ -8207,7 +8359,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="C97">
         <v>1112</v>
@@ -8275,7 +8427,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="C98">
         <v>1133</v>
@@ -8343,7 +8495,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="C99">
         <v>1137</v>
@@ -8411,7 +8563,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="C100">
         <v>925</v>
@@ -8479,7 +8631,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="C101">
         <v>631</v>
@@ -8547,7 +8699,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="C102">
         <v>1102</v>
@@ -8615,7 +8767,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="C103">
         <v>1017</v>
@@ -8683,7 +8835,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="C104">
         <v>1067</v>
@@ -8751,7 +8903,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C105">
         <v>1158</v>
@@ -8819,7 +8971,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="C106">
         <v>1161</v>
@@ -8887,7 +9039,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C107">
         <v>1177</v>
@@ -8955,7 +9107,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="C108">
         <v>1179</v>
@@ -9023,7 +9175,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="C109">
         <v>1129</v>
@@ -9091,7 +9243,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="C110">
         <v>929</v>
@@ -9159,7 +9311,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="C111">
         <v>623</v>
@@ -9227,7 +9379,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="C112">
         <v>916</v>
@@ -9295,7 +9447,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="C113">
         <v>751</v>
@@ -9363,7 +9515,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="C114">
         <v>1088</v>
@@ -9431,7 +9583,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="C115">
         <v>895</v>
@@ -9499,7 +9651,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="C116">
         <v>1159</v>
@@ -9567,7 +9719,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="C117">
         <v>797</v>
@@ -9635,7 +9787,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="C118">
         <v>854</v>
@@ -9703,7 +9855,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="C119">
         <v>1159</v>
@@ -9771,7 +9923,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="C120">
         <v>1229</v>
@@ -9839,7 +9991,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="C121">
         <v>1074</v>
@@ -9907,7 +10059,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="C122">
         <v>1203</v>
@@ -9975,7 +10127,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="C123">
         <v>1101</v>
@@ -10043,7 +10195,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="C124">
         <v>1130</v>
@@ -10111,7 +10263,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>125</v>
+        <v>146</v>
       </c>
       <c r="C125">
         <v>1167</v>
@@ -10179,7 +10331,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C126">
         <v>1119</v>
@@ -10247,7 +10399,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>127</v>
+        <v>148</v>
       </c>
       <c r="C127">
         <v>1163</v>
@@ -10315,7 +10467,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="C128">
         <v>1094</v>
@@ -10383,7 +10535,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>129</v>
+        <v>150</v>
       </c>
       <c r="C129">
         <v>1089</v>
@@ -10451,7 +10603,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="C130">
         <v>1098</v>
@@ -10519,7 +10671,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C131">
         <v>966</v>
@@ -10587,7 +10739,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="C132">
         <v>1076</v>
@@ -10655,7 +10807,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="C133">
         <v>1009</v>
@@ -10723,7 +10875,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C134">
         <v>954</v>
@@ -10791,7 +10943,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="C135">
         <v>1094</v>
@@ -10859,7 +11011,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="C136">
         <v>1122</v>
@@ -10927,7 +11079,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="C137">
         <v>1164</v>
@@ -10995,7 +11147,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="C138">
         <v>988</v>
@@ -11063,7 +11215,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C139">
         <v>996</v>
@@ -11131,7 +11283,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="C140">
         <v>1155</v>
@@ -11199,7 +11351,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="C141">
         <v>732</v>
@@ -11267,7 +11419,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="C142">
         <v>966</v>
@@ -11335,7 +11487,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="C143">
         <v>994</v>
@@ -11403,7 +11555,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="C144">
         <v>830</v>
@@ -11471,7 +11623,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="C145">
         <v>854</v>
@@ -11539,7 +11691,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>146</v>
+        <v>167</v>
       </c>
       <c r="C146">
         <v>785</v>
@@ -11607,7 +11759,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="C147">
         <v>1158</v>
@@ -11675,7 +11827,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="C148">
         <v>1200</v>
@@ -11743,7 +11895,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="C149">
         <v>1149</v>
@@ -11811,7 +11963,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="C150">
         <v>1191</v>
@@ -11879,7 +12031,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="C151">
         <v>1116</v>
@@ -11947,7 +12099,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="C152">
         <v>1048</v>
@@ -12015,7 +12167,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="C153">
         <v>1211</v>
@@ -12083,7 +12235,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="C154">
         <v>1190</v>
@@ -12151,7 +12303,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="C155">
         <v>971</v>
@@ -12219,7 +12371,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
       <c r="C156">
         <v>1060</v>
@@ -12287,7 +12439,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C157">
         <v>1175</v>
@@ -12355,7 +12507,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="C158">
         <v>1016</v>
@@ -12423,7 +12575,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="C159">
         <v>1155</v>
@@ -12491,7 +12643,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>160</v>
+        <v>181</v>
       </c>
       <c r="C160">
         <v>812</v>
@@ -12559,7 +12711,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>161</v>
+        <v>182</v>
       </c>
       <c r="C161">
         <v>671</v>
@@ -12627,7 +12779,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>162</v>
+        <v>183</v>
       </c>
       <c r="C162">
         <v>897</v>
@@ -12695,7 +12847,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="C163">
         <v>785</v>
@@ -12763,7 +12915,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="C164">
         <v>768</v>
@@ -12831,7 +12983,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="C165">
         <v>1080</v>
@@ -12899,7 +13051,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>166</v>
+        <v>187</v>
       </c>
       <c r="C166">
         <v>940</v>
@@ -12967,7 +13119,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="C167">
         <v>1190</v>
@@ -13035,7 +13187,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>168</v>
+        <v>189</v>
       </c>
       <c r="C168">
         <v>1082</v>
@@ -13103,7 +13255,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>169</v>
+        <v>190</v>
       </c>
       <c r="C169">
         <v>830</v>
@@ -13171,7 +13323,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>170</v>
+        <v>191</v>
       </c>
       <c r="C170">
         <v>1109</v>
@@ -13239,7 +13391,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>171</v>
+        <v>192</v>
       </c>
       <c r="C171">
         <v>786</v>
@@ -13307,7 +13459,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="C172">
         <v>929</v>
@@ -13375,7 +13527,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="C173">
         <v>1146</v>
@@ -13443,7 +13595,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="C174">
         <v>1035</v>
@@ -13511,7 +13663,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="C175">
         <v>927</v>
@@ -13579,7 +13731,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="C176">
         <v>1194</v>
@@ -13647,7 +13799,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="C177">
         <v>1218</v>
@@ -13715,7 +13867,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="C178">
         <v>918</v>
@@ -13783,7 +13935,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="C179">
         <v>1092</v>
@@ -13851,7 +14003,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="C180">
         <v>1040</v>
@@ -13919,7 +14071,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="C181">
         <v>1180</v>
@@ -13987,7 +14139,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="C182">
         <v>1187</v>
@@ -14055,7 +14207,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="C183">
         <v>1140</v>
@@ -14123,7 +14275,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="C184">
         <v>1033</v>
@@ -14191,7 +14343,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>185</v>
+        <v>206</v>
       </c>
       <c r="C185">
         <v>940</v>
@@ -14259,7 +14411,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="C186">
         <v>796</v>
@@ -14327,7 +14479,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="C187">
         <v>1146</v>
@@ -14395,7 +14547,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="C188">
         <v>1205</v>
@@ -14463,7 +14615,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>189</v>
+        <v>210</v>
       </c>
       <c r="C189">
         <v>885</v>
@@ -14531,7 +14683,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="C190">
         <v>1194</v>
@@ -14599,7 +14751,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="C191">
         <v>1226</v>
@@ -14667,7 +14819,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="C192">
         <v>1024</v>
@@ -14735,7 +14887,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>193</v>
+        <v>214</v>
       </c>
       <c r="C193">
         <v>1112</v>
@@ -14803,7 +14955,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="C194">
         <v>1075</v>
@@ -14871,7 +15023,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>195</v>
+        <v>216</v>
       </c>
       <c r="C195">
         <v>1197</v>
@@ -14939,7 +15091,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="C196">
         <v>1100</v>
@@ -15007,7 +15159,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="C197">
         <v>780</v>
@@ -15075,7 +15227,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="C198">
         <v>1215</v>
@@ -15143,7 +15295,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="C199">
         <v>1221</v>
@@ -15211,7 +15363,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="C200">
         <v>1185</v>
@@ -15279,7 +15431,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>201</v>
+        <v>222</v>
       </c>
       <c r="C201">
         <v>1113</v>
@@ -15347,7 +15499,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="C202">
         <v>998</v>
@@ -15415,7 +15567,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="C203">
         <v>1055</v>
@@ -15483,7 +15635,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="C204">
         <v>1156</v>
@@ -15551,7 +15703,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="C205">
         <v>1027</v>
@@ -15619,7 +15771,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="C206">
         <v>1208</v>
@@ -15687,7 +15839,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="C207">
         <v>914</v>
@@ -15755,7 +15907,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="C208">
         <v>887</v>
@@ -15823,7 +15975,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
       <c r="C209">
         <v>740</v>
@@ -15891,7 +16043,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="C210">
         <v>1051</v>
@@ -15959,7 +16111,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="C211">
         <v>1183</v>
@@ -16027,7 +16179,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="C212">
         <v>870</v>
@@ -16095,7 +16247,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>213</v>
+        <v>234</v>
       </c>
       <c r="C213">
         <v>1009</v>
@@ -16163,7 +16315,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="C214">
         <v>1164</v>
@@ -16231,7 +16383,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="C215">
         <v>1182</v>
@@ -16299,7 +16451,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="C216">
         <v>1146</v>
@@ -16367,7 +16519,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>217</v>
+        <v>238</v>
       </c>
       <c r="C217">
         <v>1125</v>
@@ -16435,7 +16587,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="C218">
         <v>1106</v>
@@ -16503,7 +16655,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="C219">
         <v>1005</v>
@@ -16571,7 +16723,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>220</v>
+        <v>241</v>
       </c>
       <c r="C220">
         <v>1104</v>
@@ -16639,7 +16791,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>221</v>
+        <v>242</v>
       </c>
       <c r="C221">
         <v>1205</v>
@@ -16707,7 +16859,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>222</v>
+        <v>243</v>
       </c>
       <c r="C222">
         <v>1090</v>
@@ -16775,7 +16927,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>223</v>
+        <v>244</v>
       </c>
       <c r="C223">
         <v>1065</v>
@@ -16843,7 +16995,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>224</v>
+        <v>245</v>
       </c>
       <c r="C224">
         <v>1088</v>
@@ -16911,7 +17063,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="C225">
         <v>1039</v>
@@ -16979,7 +17131,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>226</v>
+        <v>247</v>
       </c>
       <c r="C226">
         <v>1181</v>
@@ -17047,7 +17199,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>227</v>
+        <v>248</v>
       </c>
       <c r="C227">
         <v>1018</v>
@@ -17115,7 +17267,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>228</v>
+        <v>249</v>
       </c>
       <c r="C228">
         <v>754</v>
@@ -17183,7 +17335,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>229</v>
+        <v>250</v>
       </c>
       <c r="C229">
         <v>1075</v>
@@ -17251,7 +17403,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="C230">
         <v>1106</v>
@@ -17319,7 +17471,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="C231">
         <v>821</v>
@@ -17387,7 +17539,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>232</v>
+        <v>253</v>
       </c>
       <c r="C232">
         <v>1007</v>
@@ -17455,7 +17607,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>233</v>
+        <v>254</v>
       </c>
       <c r="C233">
         <v>717</v>
@@ -17523,7 +17675,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>234</v>
+        <v>255</v>
       </c>
       <c r="C234">
         <v>490</v>
@@ -17591,7 +17743,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>235</v>
+        <v>256</v>
       </c>
       <c r="C235">
         <v>965</v>
@@ -17659,7 +17811,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="C236">
         <v>531</v>
@@ -17727,7 +17879,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>237</v>
+        <v>258</v>
       </c>
       <c r="C237">
         <v>771</v>
@@ -17795,7 +17947,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>238</v>
+        <v>259</v>
       </c>
       <c r="C238">
         <v>659</v>
@@ -17863,7 +18015,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>239</v>
+        <v>260</v>
       </c>
       <c r="C239">
         <v>1163</v>
@@ -17931,7 +18083,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>240</v>
+        <v>261</v>
       </c>
       <c r="C240">
         <v>704</v>
@@ -17999,7 +18151,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="C241">
         <v>567</v>
@@ -18067,7 +18219,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>242</v>
+        <v>263</v>
       </c>
       <c r="C242">
         <v>770</v>
@@ -18135,7 +18287,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>243</v>
+        <v>264</v>
       </c>
       <c r="C243">
         <v>264</v>
@@ -18203,7 +18355,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="C244">
         <v>771</v>
@@ -18271,7 +18423,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>245</v>
+        <v>266</v>
       </c>
       <c r="C245">
         <v>736</v>
@@ -18339,7 +18491,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="C246">
         <v>721</v>
@@ -18407,7 +18559,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="C247">
         <v>664</v>
@@ -18475,7 +18627,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="C248">
         <v>1159</v>
@@ -18543,7 +18695,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="C249">
         <v>1216</v>
@@ -18611,7 +18763,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="C250">
         <v>1185</v>
@@ -18679,7 +18831,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="C251">
         <v>1071</v>
@@ -18747,7 +18899,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>252</v>
+        <v>273</v>
       </c>
       <c r="C252">
         <v>859</v>
@@ -18815,7 +18967,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>253</v>
+        <v>274</v>
       </c>
       <c r="C253">
         <v>962</v>
@@ -18883,7 +19035,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="C254">
         <v>1187</v>
@@ -18951,7 +19103,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>255</v>
+        <v>276</v>
       </c>
       <c r="C255">
         <v>987</v>
@@ -19019,7 +19171,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="C256">
         <v>603</v>
@@ -19087,7 +19239,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="C257">
         <v>1101</v>
@@ -19155,7 +19307,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="C258">
         <v>1102</v>
@@ -19223,7 +19375,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="C259">
         <v>1108</v>
@@ -19291,7 +19443,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="C260">
         <v>927</v>
@@ -19359,7 +19511,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="C261">
         <v>1004</v>
@@ -19427,7 +19579,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>283</v>
       </c>
       <c r="C262">
         <v>1048</v>
@@ -19495,7 +19647,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="C263">
         <v>960</v>
@@ -19563,7 +19715,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>264</v>
+        <v>285</v>
       </c>
       <c r="C264">
         <v>690</v>
@@ -19631,7 +19783,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="C265">
         <v>884</v>
@@ -19699,7 +19851,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="C266">
         <v>780</v>
@@ -19767,7 +19919,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="C267">
         <v>1212</v>
@@ -19835,7 +19987,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="C268">
         <v>1159</v>
@@ -19903,7 +20055,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>269</v>
+        <v>290</v>
       </c>
       <c r="C269">
         <v>1156</v>
@@ -19971,7 +20123,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>270</v>
+        <v>291</v>
       </c>
       <c r="C270">
         <v>956</v>
@@ -20039,7 +20191,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="C271">
         <v>715</v>
@@ -20107,7 +20259,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>272</v>
+        <v>293</v>
       </c>
       <c r="C272">
         <v>1056</v>
@@ -20175,7 +20327,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>273</v>
+        <v>294</v>
       </c>
       <c r="C273">
         <v>673</v>
@@ -20243,7 +20395,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="C274">
         <v>903</v>
@@ -20311,7 +20463,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>275</v>
+        <v>296</v>
       </c>
       <c r="C275">
         <v>616</v>
@@ -20379,7 +20531,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="C276">
         <v>938</v>
@@ -20447,7 +20599,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>277</v>
+        <v>298</v>
       </c>
       <c r="C277">
         <v>754</v>
@@ -20515,7 +20667,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>278</v>
+        <v>299</v>
       </c>
       <c r="C278">
         <v>674</v>
@@ -20583,7 +20735,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>279</v>
+        <v>300</v>
       </c>
       <c r="C279">
         <v>856</v>
@@ -20651,7 +20803,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>280</v>
+        <v>301</v>
       </c>
       <c r="C280">
         <v>860</v>
@@ -20719,7 +20871,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
       <c r="C281">
         <v>461</v>
@@ -20787,7 +20939,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="C282">
         <v>1060</v>
@@ -20855,7 +21007,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>283</v>
+        <v>304</v>
       </c>
       <c r="C283">
         <v>1179</v>
@@ -20923,7 +21075,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>284</v>
+        <v>305</v>
       </c>
       <c r="C284">
         <v>1175</v>
@@ -20991,7 +21143,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="C285">
         <v>682</v>
@@ -21059,7 +21211,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>286</v>
+        <v>307</v>
       </c>
       <c r="C286">
         <v>933</v>
@@ -21127,7 +21279,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>287</v>
+        <v>308</v>
       </c>
       <c r="C287">
         <v>1181</v>
@@ -21195,7 +21347,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="C288">
         <v>1152</v>
@@ -21263,7 +21415,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="C289">
         <v>1107</v>
@@ -21331,7 +21483,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>290</v>
+        <v>311</v>
       </c>
       <c r="C290">
         <v>1151</v>
@@ -21399,7 +21551,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>291</v>
+        <v>312</v>
       </c>
       <c r="C291">
         <v>1177</v>
@@ -21467,7 +21619,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>292</v>
+        <v>313</v>
       </c>
       <c r="C292">
         <v>1133</v>
@@ -21535,7 +21687,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>293</v>
+        <v>314</v>
       </c>
       <c r="C293">
         <v>1078</v>
@@ -21603,7 +21755,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>294</v>
+        <v>315</v>
       </c>
       <c r="C294">
         <v>1080</v>
@@ -21671,7 +21823,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>316</v>
       </c>
       <c r="C295">
         <v>1179</v>
@@ -21739,7 +21891,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="C296">
         <v>1063</v>
@@ -21807,7 +21959,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>297</v>
+        <v>318</v>
       </c>
       <c r="C297">
         <v>1058</v>
@@ -21875,7 +22027,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>298</v>
+        <v>319</v>
       </c>
       <c r="C298">
         <v>1134</v>
@@ -21943,7 +22095,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>299</v>
+        <v>320</v>
       </c>
       <c r="C299">
         <v>1062</v>
@@ -22011,7 +22163,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>300</v>
+        <v>321</v>
       </c>
       <c r="C300">
         <v>745</v>
@@ -22079,7 +22231,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>301</v>
+        <v>322</v>
       </c>
       <c r="C301">
         <v>929</v>
@@ -22147,7 +22299,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>302</v>
+        <v>323</v>
       </c>
       <c r="C302">
         <v>818</v>
@@ -22215,7 +22367,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>303</v>
+        <v>324</v>
       </c>
       <c r="C303">
         <v>1099</v>
@@ -22283,7 +22435,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="C304">
         <v>1025</v>
@@ -22351,7 +22503,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>305</v>
+        <v>326</v>
       </c>
       <c r="C305">
         <v>1011</v>
@@ -22419,7 +22571,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="C306">
         <v>1047</v>
@@ -22487,7 +22639,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>307</v>
+        <v>328</v>
       </c>
       <c r="C307">
         <v>1100</v>
@@ -22555,7 +22707,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="C308">
         <v>1108</v>
@@ -22623,7 +22775,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="C309">
         <v>1056</v>
@@ -22691,7 +22843,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>310</v>
+        <v>331</v>
       </c>
       <c r="C310">
         <v>850</v>
@@ -22759,7 +22911,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="C311">
         <v>1049</v>
@@ -22827,7 +22979,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>312</v>
+        <v>333</v>
       </c>
       <c r="C312">
         <v>864</v>
@@ -22895,7 +23047,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>313</v>
+        <v>334</v>
       </c>
       <c r="C313">
         <v>920</v>
@@ -22963,7 +23115,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>314</v>
+        <v>335</v>
       </c>
       <c r="C314">
         <v>1132</v>
@@ -23031,7 +23183,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="C315">
         <v>689</v>
@@ -23099,7 +23251,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>316</v>
+        <v>337</v>
       </c>
       <c r="C316">
         <v>764</v>
@@ -23167,7 +23319,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="C317">
         <v>1114</v>
@@ -23235,7 +23387,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>318</v>
+        <v>339</v>
       </c>
       <c r="C318">
         <v>667</v>
@@ -23303,7 +23455,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="C319">
         <v>1015</v>
@@ -23371,7 +23523,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="C320">
         <v>1161</v>
@@ -23439,7 +23591,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="C321">
         <v>1201</v>
@@ -23507,7 +23659,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>322</v>
+        <v>343</v>
       </c>
       <c r="C322">
         <v>1093</v>
@@ -23575,7 +23727,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>323</v>
+        <v>344</v>
       </c>
       <c r="C323">
         <v>1205</v>
@@ -23643,7 +23795,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>324</v>
+        <v>345</v>
       </c>
       <c r="C324">
         <v>1097</v>
@@ -23711,7 +23863,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="C325">
         <v>871</v>
@@ -23779,7 +23931,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>326</v>
+        <v>347</v>
       </c>
       <c r="C326">
         <v>641</v>
@@ -23847,7 +23999,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C327">
         <v>1052</v>
@@ -23915,7 +24067,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>328</v>
+        <v>349</v>
       </c>
       <c r="C328">
         <v>1008</v>
@@ -23983,7 +24135,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>329</v>
+        <v>350</v>
       </c>
       <c r="C329">
         <v>797</v>
@@ -24051,7 +24203,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="C330">
         <v>865</v>
@@ -24119,7 +24271,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>331</v>
+        <v>352</v>
       </c>
       <c r="C331">
         <v>876</v>
@@ -24187,7 +24339,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>332</v>
+        <v>353</v>
       </c>
       <c r="C332">
         <v>565</v>
@@ -24255,7 +24407,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>333</v>
+        <v>354</v>
       </c>
       <c r="C333">
         <v>1045</v>
@@ -24323,7 +24475,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>334</v>
+        <v>355</v>
       </c>
       <c r="C334">
         <v>895</v>
@@ -24391,7 +24543,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>335</v>
+        <v>356</v>
       </c>
       <c r="C335">
         <v>598</v>
@@ -24459,7 +24611,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="C336">
         <v>1090</v>
@@ -24527,7 +24679,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>337</v>
+        <v>358</v>
       </c>
       <c r="C337">
         <v>829</v>
@@ -24595,7 +24747,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>338</v>
+        <v>359</v>
       </c>
       <c r="C338">
         <v>895</v>
@@ -24663,7 +24815,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>339</v>
+        <v>360</v>
       </c>
       <c r="C339">
         <v>783</v>
@@ -24731,7 +24883,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>340</v>
+        <v>361</v>
       </c>
       <c r="C340">
         <v>883</v>
@@ -24799,7 +24951,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>341</v>
+        <v>362</v>
       </c>
       <c r="C341">
         <v>802</v>
@@ -24867,7 +25019,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="C342">
         <v>906</v>
@@ -24935,7 +25087,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>343</v>
+        <v>364</v>
       </c>
       <c r="C343">
         <v>1059</v>
@@ -25003,7 +25155,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="C344">
         <v>1104</v>
@@ -25071,7 +25223,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="C345">
         <v>1159</v>
@@ -25139,7 +25291,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>346</v>
+        <v>367</v>
       </c>
       <c r="C346">
         <v>1154</v>
@@ -25207,7 +25359,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>347</v>
+        <v>368</v>
       </c>
       <c r="C347">
         <v>1159</v>
@@ -25275,7 +25427,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>348</v>
+        <v>369</v>
       </c>
       <c r="C348">
         <v>1150</v>
@@ -25343,7 +25495,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>349</v>
+        <v>370</v>
       </c>
       <c r="C349">
         <v>1201</v>
@@ -25411,7 +25563,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>350</v>
+        <v>371</v>
       </c>
       <c r="C350">
         <v>1183</v>
@@ -25479,7 +25631,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>351</v>
+        <v>372</v>
       </c>
       <c r="C351">
         <v>1131</v>
@@ -25547,7 +25699,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>352</v>
+        <v>373</v>
       </c>
       <c r="C352">
         <v>1083</v>
@@ -25615,7 +25767,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="C353">
         <v>777</v>
@@ -25683,7 +25835,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>354</v>
+        <v>375</v>
       </c>
       <c r="C354">
         <v>1104</v>
@@ -25751,7 +25903,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>355</v>
+        <v>376</v>
       </c>
       <c r="C355">
         <v>1034</v>
@@ -25819,7 +25971,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>356</v>
+        <v>377</v>
       </c>
       <c r="C356">
         <v>975</v>
@@ -25887,7 +26039,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>357</v>
+        <v>378</v>
       </c>
       <c r="C357">
         <v>1069</v>
@@ -25955,7 +26107,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>358</v>
+        <v>379</v>
       </c>
       <c r="C358">
         <v>838</v>
@@ -26023,7 +26175,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
       <c r="C359">
         <v>636</v>
@@ -26091,7 +26243,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>360</v>
+        <v>381</v>
       </c>
       <c r="C360">
         <v>1198</v>
@@ -26159,7 +26311,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>361</v>
+        <v>382</v>
       </c>
       <c r="C361">
         <v>817</v>
@@ -26227,7 +26379,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>362</v>
+        <v>383</v>
       </c>
       <c r="C362">
         <v>719</v>
@@ -26295,7 +26447,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>363</v>
+        <v>384</v>
       </c>
       <c r="C363">
         <v>854</v>
@@ -26363,7 +26515,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>364</v>
+        <v>385</v>
       </c>
       <c r="C364">
         <v>1081</v>
@@ -26431,7 +26583,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>365</v>
+        <v>386</v>
       </c>
       <c r="C365">
         <v>1185</v>
@@ -26499,7 +26651,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>366</v>
+        <v>387</v>
       </c>
       <c r="C366">
         <v>917</v>
@@ -26567,7 +26719,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>367</v>
+        <v>388</v>
       </c>
       <c r="C367">
         <v>1029</v>
@@ -26635,7 +26787,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>368</v>
+        <v>389</v>
       </c>
       <c r="C368">
         <v>1073</v>
@@ -26703,7 +26855,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>369</v>
+        <v>390</v>
       </c>
       <c r="C369">
         <v>916</v>
@@ -26771,7 +26923,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>370</v>
+        <v>391</v>
       </c>
       <c r="C370">
         <v>1155</v>
@@ -26839,7 +26991,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="C371">
         <v>540</v>
@@ -26907,7 +27059,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>372</v>
+        <v>393</v>
       </c>
       <c r="C372">
         <v>820</v>
@@ -26975,7 +27127,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>373</v>
+        <v>394</v>
       </c>
       <c r="C373">
         <v>1206</v>
@@ -27043,7 +27195,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>374</v>
+        <v>395</v>
       </c>
       <c r="C374">
         <v>1068</v>
@@ -27111,7 +27263,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>375</v>
+        <v>396</v>
       </c>
       <c r="C375">
         <v>626</v>
@@ -27179,7 +27331,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>376</v>
+        <v>397</v>
       </c>
       <c r="C376">
         <v>1157</v>
@@ -27247,7 +27399,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>377</v>
+        <v>398</v>
       </c>
       <c r="C377">
         <v>757</v>
@@ -27315,7 +27467,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>378</v>
+        <v>399</v>
       </c>
       <c r="C378">
         <v>916</v>
@@ -27383,7 +27535,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>379</v>
+        <v>400</v>
       </c>
       <c r="C379">
         <v>961</v>
@@ -27451,7 +27603,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>380</v>
+        <v>401</v>
       </c>
       <c r="C380">
         <v>1106</v>
@@ -27519,7 +27671,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>381</v>
+        <v>402</v>
       </c>
       <c r="C381">
         <v>1063</v>
@@ -27587,7 +27739,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>382</v>
+        <v>403</v>
       </c>
       <c r="C382">
         <v>1140</v>
@@ -27655,7 +27807,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>383</v>
+        <v>404</v>
       </c>
       <c r="C383">
         <v>1141</v>
@@ -27723,7 +27875,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>384</v>
+        <v>405</v>
       </c>
       <c r="C384">
         <v>1229</v>
@@ -27791,7 +27943,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>385</v>
+        <v>406</v>
       </c>
       <c r="C385">
         <v>1194</v>
@@ -27859,7 +28011,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>386</v>
+        <v>407</v>
       </c>
       <c r="C386">
         <v>1089</v>
@@ -27927,7 +28079,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>387</v>
+        <v>408</v>
       </c>
       <c r="C387">
         <v>744</v>
@@ -27995,7 +28147,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>388</v>
+        <v>409</v>
       </c>
       <c r="C388">
         <v>1037</v>
@@ -28063,7 +28215,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>389</v>
+        <v>410</v>
       </c>
       <c r="C389">
         <v>973</v>
@@ -28131,7 +28283,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>390</v>
+        <v>411</v>
       </c>
       <c r="C390">
         <v>1141</v>
@@ -28199,7 +28351,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>391</v>
+        <v>412</v>
       </c>
       <c r="C391">
         <v>1119</v>
@@ -28267,7 +28419,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>392</v>
+        <v>413</v>
       </c>
       <c r="C392">
         <v>1099</v>
@@ -28335,7 +28487,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>393</v>
+        <v>414</v>
       </c>
       <c r="C393">
         <v>1185</v>
@@ -28403,7 +28555,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>394</v>
+        <v>415</v>
       </c>
       <c r="C394">
         <v>1174</v>
@@ -28471,7 +28623,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>395</v>
+        <v>416</v>
       </c>
       <c r="C395">
         <v>1012</v>
@@ -28539,7 +28691,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>396</v>
+        <v>417</v>
       </c>
       <c r="C396">
         <v>1093</v>
@@ -28607,7 +28759,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>397</v>
+        <v>418</v>
       </c>
       <c r="C397">
         <v>783</v>
@@ -28675,7 +28827,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>398</v>
+        <v>419</v>
       </c>
       <c r="C398">
         <v>1174</v>
@@ -28743,7 +28895,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="C399">
         <v>998</v>
@@ -28811,7 +28963,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>400</v>
+        <v>421</v>
       </c>
       <c r="C400">
         <v>1123</v>
@@ -28879,7 +29031,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>401</v>
+        <v>422</v>
       </c>
       <c r="C401">
         <v>573</v>
@@ -28947,7 +29099,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>402</v>
+        <v>423</v>
       </c>
       <c r="C402">
         <v>1087</v>
@@ -29015,7 +29167,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>403</v>
+        <v>424</v>
       </c>
       <c r="C403">
         <v>1072</v>
@@ -29083,7 +29235,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="C404">
         <v>1117</v>
@@ -29151,7 +29303,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>405</v>
+        <v>426</v>
       </c>
       <c r="C405">
         <v>1117</v>
@@ -29219,7 +29371,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>406</v>
+        <v>427</v>
       </c>
       <c r="C406">
         <v>1117</v>
@@ -29287,7 +29439,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>407</v>
+        <v>428</v>
       </c>
       <c r="C407">
         <v>1175</v>
@@ -29355,7 +29507,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>408</v>
+        <v>429</v>
       </c>
       <c r="C408">
         <v>1170</v>
@@ -29423,7 +29575,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>409</v>
+        <v>430</v>
       </c>
       <c r="C409">
         <v>1183</v>
@@ -29491,7 +29643,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>410</v>
+        <v>431</v>
       </c>
       <c r="C410">
         <v>1053</v>
@@ -29559,7 +29711,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>411</v>
+        <v>432</v>
       </c>
       <c r="C411">
         <v>1106</v>
@@ -29627,7 +29779,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>412</v>
+        <v>433</v>
       </c>
       <c r="C412">
         <v>994</v>
@@ -29695,7 +29847,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>413</v>
+        <v>434</v>
       </c>
       <c r="C413">
         <v>1186</v>
@@ -29763,7 +29915,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="C414">
         <v>899</v>
@@ -29831,7 +29983,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>415</v>
+        <v>436</v>
       </c>
       <c r="C415">
         <v>1210</v>
@@ -29899,7 +30051,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>416</v>
+        <v>437</v>
       </c>
       <c r="C416">
         <v>997</v>
@@ -29967,7 +30119,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>417</v>
+        <v>438</v>
       </c>
       <c r="C417">
         <v>1173</v>
@@ -30035,7 +30187,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>418</v>
+        <v>439</v>
       </c>
       <c r="C418">
         <v>1081</v>
@@ -30103,7 +30255,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="C419">
         <v>1065</v>
@@ -30171,7 +30323,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>420</v>
+        <v>441</v>
       </c>
       <c r="C420">
         <v>844</v>
@@ -30239,7 +30391,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>421</v>
+        <v>442</v>
       </c>
       <c r="C421">
         <v>727</v>
@@ -30307,7 +30459,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>422</v>
+        <v>443</v>
       </c>
       <c r="C422">
         <v>1218</v>
@@ -30375,7 +30527,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>423</v>
+        <v>444</v>
       </c>
       <c r="C423">
         <v>1130</v>
@@ -30443,7 +30595,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>424</v>
+        <v>445</v>
       </c>
       <c r="C424">
         <v>787</v>
@@ -30511,7 +30663,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>425</v>
+        <v>446</v>
       </c>
       <c r="C425">
         <v>753</v>
@@ -30579,7 +30731,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>426</v>
+        <v>447</v>
       </c>
       <c r="C426">
         <v>1043</v>
@@ -30647,7 +30799,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>427</v>
+        <v>448</v>
       </c>
       <c r="C427">
         <v>1172</v>
@@ -30715,7 +30867,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="C428">
         <v>1164</v>
@@ -30783,7 +30935,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>429</v>
+        <v>450</v>
       </c>
       <c r="C429">
         <v>1174</v>
@@ -30851,7 +31003,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>430</v>
+        <v>451</v>
       </c>
       <c r="C430">
         <v>1177</v>
@@ -30919,7 +31071,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>431</v>
+        <v>452</v>
       </c>
       <c r="C431">
         <v>1077</v>
@@ -30987,7 +31139,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>432</v>
+        <v>453</v>
       </c>
       <c r="C432">
         <v>919</v>
@@ -31055,7 +31207,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>433</v>
+        <v>454</v>
       </c>
       <c r="C433">
         <v>1079</v>
@@ -31123,7 +31275,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>434</v>
+        <v>455</v>
       </c>
       <c r="C434">
         <v>969</v>
@@ -31191,7 +31343,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>435</v>
+        <v>456</v>
       </c>
       <c r="C435">
         <v>1167</v>
@@ -31259,7 +31411,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>436</v>
+        <v>457</v>
       </c>
       <c r="C436">
         <v>998</v>
@@ -31327,7 +31479,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>437</v>
+        <v>458</v>
       </c>
       <c r="C437">
         <v>749</v>
@@ -31395,7 +31547,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>438</v>
+        <v>459</v>
       </c>
       <c r="C438">
         <v>628</v>
@@ -31463,7 +31615,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="C439">
         <v>762</v>
@@ -31531,7 +31683,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="C440">
         <v>1013</v>
@@ -31599,7 +31751,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="C441">
         <v>1174</v>
@@ -31667,7 +31819,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="C442">
         <v>1200</v>
